--- a/ptpm_pr17_Savitsin/ptpm_pr19_Savitsin.xlsx
+++ b/ptpm_pr17_Savitsin/ptpm_pr19_Savitsin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Савицин ПР-21\ptpm_pr17_Savitsin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C52E44D-8A78-4D2F-8DDF-58FFACFD355A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62DD54FC-B43A-4111-A639-F4818E5FA0A2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="11985" windowHeight="8325" xr2:uid="{3FB8B73F-EAD9-46CC-8CF3-111BFE2B5C48}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="142">
   <si>
     <t>Задание:</t>
   </si>
@@ -105,21 +105,12 @@
     <t>Surname</t>
   </si>
   <si>
-    <t>Surname - фамилия студента, строка, 2 сим. &lt; Surname &lt;= 50 сим.</t>
-  </si>
-  <si>
     <t>Course - курс студента, целое, 0&lt;Course&lt;=4</t>
   </si>
   <si>
-    <t>Строка, 2 сим. &lt; Surname &lt;= 50 сим.</t>
-  </si>
-  <si>
     <t>Speciality</t>
   </si>
   <si>
-    <t>Строка, 10 сим. &lt; Speciality &lt;= 50 сим.</t>
-  </si>
-  <si>
     <t>Course</t>
   </si>
   <si>
@@ -141,15 +132,6 @@
     <t>Взаимозависимость</t>
   </si>
   <si>
-    <t>Целое (17)                                                                                                            0&lt;Course&lt;=4 (18)</t>
-  </si>
-  <si>
-    <t>Целое (34)                                                                                                                    PaySemester &gt; 0 (35)</t>
-  </si>
-  <si>
-    <t>Целое (38)                                                                                         DepositedAmount &gt; 0 (39)</t>
-  </si>
-  <si>
     <t>Строка,                                                                                                                  BudOrCom = бюджетный,                                                                                    BudOrCom = коммерческий</t>
   </si>
   <si>
@@ -165,15 +147,6 @@
     <t>Целое,                                                                                             DepositedAmount &gt; 0</t>
   </si>
   <si>
-    <t>другого типа (19)                                                                                                                               Course &lt;= 0 (20)                                                                                                                                    Course &gt; 4 (21)</t>
-  </si>
-  <si>
-    <t>другого типа (36)                                                                                                                         PaySemester &lt;= 0 (37)</t>
-  </si>
-  <si>
-    <t>другого типа (40)                                                                                                       DepositedAmount &lt;= 0 (41)</t>
-  </si>
-  <si>
     <t>Тестовые случаи</t>
   </si>
   <si>
@@ -186,27 +159,6 @@
     <t>Выходные данные</t>
   </si>
   <si>
-    <t>Speciality- специальность студента, строка, 5 сим. &lt; Speciality &lt;= 50 сим.</t>
-  </si>
-  <si>
-    <t>BudOrCom = бюджетный Surname = Иванов    Speciality = программист Course = 2                     FullOrPart = очное LivesDormitory = да</t>
-  </si>
-  <si>
-    <t>1, 2, 7, 8, 12, 13, 17, 18, 22, 23, 28, 29, 42</t>
-  </si>
-  <si>
-    <t>BudOrCom = коммерческий Surname = Иванов    Speciality = программист Course = 3                     FullOrPart = заочное PaySemester = 10000 DepositedAmount = 10000</t>
-  </si>
-  <si>
-    <t>BudOrCom = 3              Surname = Иванов    Speciality = программист Course = 2                     FullOrPart = очное LivesDormitory = да</t>
-  </si>
-  <si>
-    <t>BudOrCom = бюджетный Surname = А                   Speciality = программист Course = 2                     FullOrPart = очное LivesDormitory = да</t>
-  </si>
-  <si>
-    <t>BudOrCom = бюджетный Surname = Аааааааааааааааааааааааааааааааааааааааааааааааааааа Speciality = программист Course = 2                     FullOrPart = очное LivesDormitory = да</t>
-  </si>
-  <si>
     <t>Все входные данные введены корректно =&gt; Сохранение студента</t>
   </si>
   <si>
@@ -216,70 +168,312 @@
     <t>Все входные данные введены корректно =&gt; Сохранение студента Не все входные данные введены корректно =&gt; Сообщение об ошибке</t>
   </si>
   <si>
-    <t>Все входные данные введены корректно =&gt; Сохранение студента (42)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Не все входные данные введены корректно =&gt; Сообщение об ошибке (43)</t>
-  </si>
-  <si>
-    <t>1, 3, 7, 8, 12, 13, 17, 18, 22, 24, 34, 35, 38, 39, 42</t>
-  </si>
-  <si>
     <t>BudOrCom = бюджетный Surname = Иванов    Speciality = программист Course = 2                     FullOrPart = очное LivesDormitory = нет</t>
   </si>
   <si>
-    <t>1, 2, 7, 8, 12, 13, 17, 18, 22, 23, 28, 30, 42</t>
-  </si>
-  <si>
-    <t>4, 5, 6, 43</t>
-  </si>
-  <si>
-    <t>5, 6, 43</t>
-  </si>
-  <si>
-    <t>9, 43</t>
-  </si>
-  <si>
-    <t>10, 43</t>
-  </si>
-  <si>
-    <t>11, 43</t>
-  </si>
-  <si>
     <t>Не пустая строка (1)                                                                                                      BudOrCom = бюджетный (2)                                                                                        BudOrCom = коммерческий (3)</t>
   </si>
   <si>
-    <t>Пустая строка (4)                                                                                                                                            BudOrCom != бюджетный (5)                                                                                                                                    BudOrCom != коммерческий (6)</t>
-  </si>
-  <si>
-    <t>Не пустая строка (7)                                                                                                                               2 сим. &lt; Surname &lt;= 50 сим. (8)</t>
-  </si>
-  <si>
-    <t>Пустая строка (9)                                                                                                                            Surname &lt;= 2 сим. (10)                                                                                                                 Surname &gt; 50 сим. (11)</t>
-  </si>
-  <si>
-    <t>Пустая строка (14)                                                                                                                           Speciality &lt;= 5 сим. (15)                                                                                                                         Speciality &gt; 50 сим. (16)</t>
-  </si>
-  <si>
-    <t>Пустая строка (25)                                                                                                                             FullOrPart != очное (26)                                                                                                                                      FullOrPart != заочное (27)</t>
-  </si>
-  <si>
-    <t>Пустая строка (31)                                                                                                                                                 LivesDormitory != да (32)                                                                                                                       LivesDormitory != нет (33)</t>
-  </si>
-  <si>
-    <t>Не пустая строка (12)                                                                                                                          5 сим. &lt; Speciality &lt;= 50 сим. (13)</t>
-  </si>
-  <si>
-    <t>Не пустая строка (22)                                                                                                              FullOrPart = очное (23)                                                                                           FullOrPart = заочное (24)</t>
-  </si>
-  <si>
-    <t>Не пустая строка (28)                                                                                                       LivesDormitory = да (29)                                                                            LivesDormitory = нет (30)</t>
-  </si>
-  <si>
-    <t>BudOrCom =  ""              Surname = Иванов    Speciality = программист Course = 2                     FullOrPart = очное LivesDormitory = да</t>
-  </si>
-  <si>
-    <t>BudOrCom = бюджетный Surname =  ""                  Speciality = программист Course = 2                     FullOrPart = очное LivesDormitory = да</t>
+    <t>Пустая строка (4)                                                                                                                                            BudOrCom != бюджетный &amp; BudOrCom != коммерческий (5)</t>
+  </si>
+  <si>
+    <t>Surname - фамилия студента, строка, 2 сим. &lt; Surname &lt;= 50 сим., допустимы буквы и пробелы</t>
+  </si>
+  <si>
+    <t>Speciality- специальность студента, строка, 5 сим. &lt; Speciality &lt;= 50 сим., допустимы буквы и пробелы</t>
+  </si>
+  <si>
+    <t>Строка, 2 сим. &lt; Surname &lt;= 50 сим., допустимы буквы и пробелы</t>
+  </si>
+  <si>
+    <t>BudOrCom = бюджетный Surname = Ан              Speciality = прогр               Course = 1                     FullOrPart = очное LivesDormitory = да</t>
+  </si>
+  <si>
+    <t>BudOrCom = коммерческий Surname = Иванов                    Speciality = программист            Course = 3                     FullOrPart = очное PaySemester = 100000 DepositedAmount = 100000</t>
+  </si>
+  <si>
+    <t>BudOrCom = ""                Surname = Иванов    Speciality = программист Course = 2                     FullOrPart = очное LivesDormitory = нет</t>
+  </si>
+  <si>
+    <t>BudOrCom = абвг                Surname = Иванов    Speciality = программист Course = 2                     FullOrPart = очное LivesDormitory = нет</t>
+  </si>
+  <si>
+    <t>Статус студента некорректный (С)</t>
+  </si>
+  <si>
+    <t>Специальность студента некорректная(E)</t>
+  </si>
+  <si>
+    <t>BudOrCom = бюджетный                Surname = ""                 Speciality = программист Course = 2                     FullOrPart = очное LivesDormitory = нет</t>
+  </si>
+  <si>
+    <t>BudOrCom = бюджетный                Surname = А                 Speciality = программист Course = 2                     FullOrPart = очное LivesDormitory = нет</t>
+  </si>
+  <si>
+    <t>BudOrCom = бюджетный                Surname = Ааааааааааааааааааааааааааааааааааааааааааааааааааааааааааааааааааааааааааааааааааааааааааааа                                 Speciality = программист Course = 2                     FullOrPart = очное LivesDormitory = нет</t>
+  </si>
+  <si>
+    <t>BudOrCom = бюджетный                Surname = 1234                 Speciality = программист Course = 2                     FullOrPart = очное LivesDormitory = нет</t>
+  </si>
+  <si>
+    <t>BudOrCom = бюджетный Surname = Ан              Speciality = ""                       Course = 1                     FullOrPart = очное LivesDormitory = да</t>
+  </si>
+  <si>
+    <t>BudOrCom = бюджетный Surname = Ан              Speciality = абвг                       Course = 1                     FullOrPart = очное LivesDormitory = да</t>
+  </si>
+  <si>
+    <t>BudOrCom = бюджетный Surname = Ан              Speciality = абвгаааааааааааааааааааааааааааааааааааааааааааааааааааааааааааааааааааааааааааа                       Course = 1                     FullOrPart = очное LivesDormitory = да</t>
+  </si>
+  <si>
+    <t>BudOrCom = бюджетный Surname = Ан              Speciality = 123455                       Course = 1                     FullOrPart = очное LivesDormitory = да</t>
+  </si>
+  <si>
+    <t>BudOrCom = бюджетный Surname = Ан              Speciality = прогр               Course = а                     FullOrPart = очное LivesDormitory = да</t>
+  </si>
+  <si>
+    <t>BudOrCom = бюджетный Surname = Ан              Speciality = прогр               Course = -1                     FullOrPart = очное LivesDormitory = да</t>
+  </si>
+  <si>
+    <t>BudOrCom = бюджетный Surname = Ан              Speciality = прогр               Course = 6                     FullOrPart = очное LivesDormitory = да</t>
+  </si>
+  <si>
+    <t>BudOrCom = бюджетный Surname = Ан              Speciality = прогр               Course = 1                     FullOrPart = ""        LivesDormitory = да</t>
+  </si>
+  <si>
+    <t>BudOrCom = бюджетный Surname = Ан              Speciality = прогр               Course = 1                     FullOrPart = абвг        LivesDormitory = да</t>
+  </si>
+  <si>
+    <t>BudOrCom = бюджетный Surname = Ан              Speciality = прогр               Course = 1                     FullOrPart = очное LivesDormitory = ""</t>
+  </si>
+  <si>
+    <t>BudOrCom = бюджетный Surname = Ан              Speciality = прогр               Course = 1                     FullOrPart = очное LivesDormitory = абвг</t>
+  </si>
+  <si>
+    <t>BudOrCom = коммерческий Surname = Иванов                    Speciality = программист            Course = 3                     FullOrPart = очное PaySemester = абв DepositedAmount = 100000</t>
+  </si>
+  <si>
+    <t>BudOrCom = коммерческий Surname = Иванов                    Speciality = программист            Course = 3                     FullOrPart = очное PaySemester = 0 DepositedAmount = 100000</t>
+  </si>
+  <si>
+    <t>BudOrCom = коммерческий Surname = Иванов                    Speciality = программист            Course = 3                     FullOrPart = очное PaySemester = 200000 DepositedAmount = 100000</t>
+  </si>
+  <si>
+    <t>BudOrCom = коммерческий Surname = Иванов                    Speciality = программист            Course = 3                     FullOrPart = очное PaySemester = 100000 DepositedAmount = абв</t>
+  </si>
+  <si>
+    <t>BudOrCom = коммерческий Surname = Иванов                    Speciality = программист            Course = 3                     FullOrPart = очное PaySemester = 100000 DepositedAmount = 0</t>
+  </si>
+  <si>
+    <t>BudOrCom = коммерческий Surname = Иванов                    Speciality = программист            Course = 3                     FullOrPart = очное PaySemester = 100000 DepositedAmount = 200000</t>
+  </si>
+  <si>
+    <t>Строка, 4 сим. &lt; Speciality &lt;= 50 сим., допустимы буквы и пробелы</t>
+  </si>
+  <si>
+    <t>Пустая строка (12)                                                                                                                            Surname &lt; 2 сим. (13)                                                                                                                 Surname &gt; 50 сим. (14)                                                                                                              другие символы(15)
+Первый символ не буква (16) 
+Последний символ не буква (17)</t>
+  </si>
+  <si>
+    <t>Пустая строка (24)                                                                                                                           Speciality &lt; 5 сим. (25)                                                                                                                         Speciality &gt; 50 сим. (26)                                                                                                                      другие символы (27)
+Первый символ не буква (28)
+Последний символ не буква (29)</t>
+  </si>
+  <si>
+    <t>Целое (30)                                                                                                            0&lt;Course&lt;=4 (31)                                                                                                         Course=1 (32)
+Course=4 (33)</t>
+  </si>
+  <si>
+    <t>Не пустая строка (6)                                                                                                                               1 сим. &lt; Surname &lt; 51 сим. (7)
+Surname=2 (8)
+Surname=50 (9)                                                                                           буквы (10)
+буквы и пробелы(11)</t>
+  </si>
+  <si>
+    <t>Не пустая строка (18)                                                                                                                          4 сим. &lt; Speciality &lt; 51 сим. (19)                                                                                                                         буквы (20)
+Speciality = 5 (21)
+Speciality = 50 (22)
+буквы и пробелы (23)</t>
+  </si>
+  <si>
+    <t>другого типа (34)                                                                                                                               Course &lt;= 0 (35)       
+Course = 0 (36)                                                                                                                             Course &gt; 4 (37)
+Course = 5 (38)</t>
+  </si>
+  <si>
+    <t>Не пустая строка (39)                                                                                                              FullOrPart = очное (40)                                                                                           FullOrPart = заочное (41)</t>
+  </si>
+  <si>
+    <t>Не пустая строка (44)                                                                                                       LivesDormitory = да (45)                                                                            LivesDormitory = нет (46)</t>
+  </si>
+  <si>
+    <t>Пустая строка (47)                                                                                                                                                 LivesDormitory != да &amp; LivesDormitory != нет (48)</t>
+  </si>
+  <si>
+    <t>другого типа (53)                                                                                                                         PaySemester &lt;= 0 (54)
+PaySemester = 0 (55)
+PaySemester &gt; 100000 (56)
+PaySemester = 100001 (57)</t>
+  </si>
+  <si>
+    <t>другого типа (62)                                                                                                       DepositedAmount &lt;= 0 (63)
+DepositedAmount = 0 (64)
+DepositedAmount &gt; 100000 (65)
+DepositedAmount = 100001 (66)</t>
+  </si>
+  <si>
+    <t>Все входные данные введены корректно =&gt; Сохранение студента (67)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Не все входные данные введены корректно =&gt; Сообщение об ошибке (68)</t>
+  </si>
+  <si>
+    <t>Пустая строка (42)                                                                                                                             FullOrPart != очное &amp; FullOrPart != заочное (43)</t>
+  </si>
+  <si>
+    <t>1, 2, 6, 7, 8, 10, 18, 19, 20, 21, 30, 31, 32, 39, 40, 44, 45, 67</t>
+  </si>
+  <si>
+    <t>BudOrCom = коммерческий Surname = Аааааааааааааааааааааааааа аааааааааааааааааааааааа                       Speciality = программистттттттттттттт ттттттттттттттттттттттттт            Course = 4                     FullOrPart = заочное PaySemester = 1 DepositedAmount = 1</t>
+  </si>
+  <si>
+    <t>1, 3, 6, 7, 9, 11, 18, 19, 22, 23, 30, 31, 33, 39, 41, 49, 50, 51, 58, 59, 60, 67</t>
+  </si>
+  <si>
+    <t>1, 2, 6, 7, 10, 18, 19, 20, 30, 31, 39, 40, 44, 46, 67</t>
+  </si>
+  <si>
+    <t>1, 3, 5, 7, 10, 18, 19, 20, 30, 31, 39, 40, 49, 50, 52, 58, 59, 61, 67</t>
+  </si>
+  <si>
+    <t>Целое (58)                                                                                                                                            1 &lt; DepositedAmount &lt;= 100001 (59)
+DepositedAmount = 1 (60)
+DepositedAmount = 100000 (61)</t>
+  </si>
+  <si>
+    <t>Целое (49)                                                                                                                                        1 &lt; PaySemester &lt; 100001 (50)
+PaySemester = 1 (51)
+PaySemester = 100000 (52)</t>
+  </si>
+  <si>
+    <t>4, 68</t>
+  </si>
+  <si>
+    <t>5, 68</t>
+  </si>
+  <si>
+    <t>12, 68</t>
+  </si>
+  <si>
+    <t>13, 68</t>
+  </si>
+  <si>
+    <t>14, 68</t>
+  </si>
+  <si>
+    <t>15, 68</t>
+  </si>
+  <si>
+    <t>24, 68</t>
+  </si>
+  <si>
+    <t>25, 68</t>
+  </si>
+  <si>
+    <t>26, 68</t>
+  </si>
+  <si>
+    <t>27, 68</t>
+  </si>
+  <si>
+    <t>34, 68</t>
+  </si>
+  <si>
+    <t>35, 68</t>
+  </si>
+  <si>
+    <t>37, 68</t>
+  </si>
+  <si>
+    <t>42, 68</t>
+  </si>
+  <si>
+    <t>43, 68</t>
+  </si>
+  <si>
+    <t>47, 68</t>
+  </si>
+  <si>
+    <t>48, 68</t>
+  </si>
+  <si>
+    <t>53, 68</t>
+  </si>
+  <si>
+    <t>54, 55, 68</t>
+  </si>
+  <si>
+    <t>56, 68</t>
+  </si>
+  <si>
+    <t>62, 68</t>
+  </si>
+  <si>
+    <t>63, 64, 68</t>
+  </si>
+  <si>
+    <t>65, 68</t>
+  </si>
+  <si>
+    <t>BudOrCom = бюджетный Surname = 1ванов    Speciality = программист Course = 2                     FullOrPart = очное LivesDormitory = нет</t>
+  </si>
+  <si>
+    <t>16, 68</t>
+  </si>
+  <si>
+    <t>BudOrCom = бюджетный Surname = Ивано1    Speciality = программист Course = 2                     FullOrPart = очное LivesDormitory = нет</t>
+  </si>
+  <si>
+    <t>17, 68</t>
+  </si>
+  <si>
+    <t>28, 68</t>
+  </si>
+  <si>
+    <t>29, 68</t>
+  </si>
+  <si>
+    <t>36, 68</t>
+  </si>
+  <si>
+    <t>38, 68</t>
+  </si>
+  <si>
+    <t>57, 66</t>
+  </si>
+  <si>
+    <t>57, 68</t>
+  </si>
+  <si>
+    <t>66, 68</t>
+  </si>
+  <si>
+    <t>BudOrCom = бюджетный Surname = Иванов    Speciality = 1рограммист Course = 2                     FullOrPart = очное LivesDormitory = нет</t>
+  </si>
+  <si>
+    <t>BudOrCom = бюджетный Surname = Иванов    Speciality = программис1 Course = 2                     FullOrPart = очное LivesDormitory = нет</t>
+  </si>
+  <si>
+    <t>BudOrCom = бюджетный Surname = Ан              Speciality = прогр               Course = 0                     FullOrPart = очное LivesDormitory = да</t>
+  </si>
+  <si>
+    <t>BudOrCom = бюджетный Surname = Ан              Speciality = прогр               Course = 5                     FullOrPart = очное LivesDormitory = да</t>
+  </si>
+  <si>
+    <t>BudOrCom = коммерческий Surname = Иванов                    Speciality = программист            Course = 3                     FullOrPart = очное PaySemester = 100001 DepositedAmount = 100000</t>
+  </si>
+  <si>
+    <t>BudOrCom = коммерческий Surname = Иванов                    Speciality = программист            Course = 3                     FullOrPart = очное PaySemester = 100000 DepositedAmount = 100001</t>
   </si>
 </sst>
 </file>
@@ -319,7 +513,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -342,11 +536,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -355,30 +586,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -694,7 +936,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E90D350-F23E-4C76-9F4E-6DE538ED19AF}">
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:O82"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="15.85546875" customWidth="1"/>
@@ -708,195 +950,195 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
@@ -912,336 +1154,336 @@
       <c r="K15" s="2"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
+      <c r="A17" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
+      <c r="A18" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="16"/>
+      <c r="K21" s="16"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B32" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10" t="s">
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="11" t="s">
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11" t="s">
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
+      <c r="L32" s="13"/>
+      <c r="M32" s="13"/>
     </row>
     <row r="33" spans="1:13" s="1" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>1</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
       <c r="E33" s="8" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="8" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="I33" s="8"/>
       <c r="J33" s="8"/>
       <c r="K33" s="8" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="L33" s="8"/>
       <c r="M33" s="8"/>
     </row>
-    <row r="34" spans="1:13" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" ht="100.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>2</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
       <c r="E34" s="8" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F34" s="8"/>
       <c r="G34" s="8"/>
       <c r="H34" s="8" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="I34" s="8"/>
       <c r="J34" s="8"/>
       <c r="K34" s="8" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="L34" s="8"/>
       <c r="M34" s="8"/>
     </row>
-    <row r="35" spans="1:13" s="1" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" s="1" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>3</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
+      <c r="B35" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
       <c r="E35" s="8" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="8" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I35" s="8"/>
       <c r="J35" s="8"/>
       <c r="K35" s="8" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="L35" s="8"/>
       <c r="M35" s="8"/>
     </row>
-    <row r="36" spans="1:13" s="1" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" s="1" customFormat="1" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>4</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
+      <c r="B36" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
       <c r="E36" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F36" s="8"/>
       <c r="G36" s="8"/>
       <c r="H36" s="8" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="I36" s="8"/>
       <c r="J36" s="8"/>
       <c r="K36" s="8" t="s">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="L36" s="8"/>
       <c r="M36" s="8"/>
@@ -1250,23 +1492,23 @@
       <c r="A37" s="5">
         <v>5</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
+      <c r="B37" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
       <c r="E37" s="8" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F37" s="8"/>
       <c r="G37" s="8"/>
       <c r="H37" s="8" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="I37" s="8"/>
       <c r="J37" s="8"/>
       <c r="K37" s="8" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="L37" s="8"/>
       <c r="M37" s="8"/>
@@ -1275,73 +1517,73 @@
       <c r="A38" s="5">
         <v>6</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
+      <c r="B38" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
       <c r="E38" s="8" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F38" s="8"/>
       <c r="G38" s="8"/>
       <c r="H38" s="8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="I38" s="8"/>
       <c r="J38" s="8"/>
       <c r="K38" s="8" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="L38" s="8"/>
       <c r="M38" s="8"/>
     </row>
-    <row r="39" spans="1:13" s="1" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" s="1" customFormat="1" ht="111.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>7</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
+      <c r="B39" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
       <c r="E39" s="8" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="F39" s="8"/>
       <c r="G39" s="8"/>
       <c r="H39" s="8" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="I39" s="8"/>
       <c r="J39" s="8"/>
       <c r="K39" s="8" t="s">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="L39" s="8"/>
       <c r="M39" s="8"/>
     </row>
-    <row r="40" spans="1:13" s="1" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" s="1" customFormat="1" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>8</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
+      <c r="B40" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
       <c r="E40" s="8" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F40" s="8"/>
       <c r="G40" s="8"/>
       <c r="H40" s="8" t="s">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="I40" s="8"/>
       <c r="J40" s="8"/>
       <c r="K40" s="8" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="L40" s="8"/>
       <c r="M40" s="8"/>
@@ -1350,75 +1592,75 @@
       <c r="A41" s="5">
         <v>9</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
+      <c r="B41" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
       <c r="E41" s="8" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="F41" s="8"/>
       <c r="G41" s="8"/>
       <c r="H41" s="8" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="I41" s="8"/>
       <c r="J41" s="8"/>
       <c r="K41" s="8" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="L41" s="8"/>
       <c r="M41" s="8"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A43" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="B43" s="18"/>
-      <c r="C43" s="18"/>
-      <c r="D43" s="18"/>
-      <c r="E43" s="18"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18"/>
-      <c r="H43" s="18"/>
-      <c r="I43" s="18"/>
-      <c r="J43" s="18"/>
-      <c r="K43" s="18"/>
-      <c r="L43" s="18"/>
-      <c r="M43" s="18"/>
+      <c r="A43" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B43" s="15"/>
+      <c r="C43" s="15"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="15"/>
+      <c r="H43" s="15"/>
+      <c r="I43" s="15"/>
+      <c r="J43" s="15"/>
+      <c r="K43" s="15"/>
+      <c r="L43" s="15"/>
+      <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B44" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C44" s="11"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F44" s="13"/>
+      <c r="G44" s="13"/>
+      <c r="H44" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="I44" s="11"/>
-      <c r="J44" s="11"/>
-      <c r="K44" s="11" t="s">
+      <c r="I44" s="13"/>
+      <c r="J44" s="13"/>
+      <c r="K44" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="L44" s="11"/>
-      <c r="M44" s="11"/>
+      <c r="L44" s="13"/>
+      <c r="M44" s="13"/>
     </row>
     <row r="45" spans="1:13" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <v>1</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
@@ -1428,7 +1670,7 @@
       <c r="F45" s="8"/>
       <c r="G45" s="8"/>
       <c r="H45" s="8" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="I45" s="8"/>
       <c r="J45" s="8"/>
@@ -1436,12 +1678,12 @@
       <c r="L45" s="8"/>
       <c r="M45" s="8"/>
     </row>
-    <row r="46" spans="1:13" s="1" customFormat="1" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" s="1" customFormat="1" ht="224.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
         <v>2</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
@@ -1451,7 +1693,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="8"/>
       <c r="H46" s="8" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="I46" s="8"/>
       <c r="J46" s="8"/>
@@ -1464,7 +1706,7 @@
         <v>3</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="C47" s="8"/>
       <c r="D47" s="8"/>
@@ -1474,7 +1716,7 @@
       <c r="F47" s="8"/>
       <c r="G47" s="8"/>
       <c r="H47" s="8" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="I47" s="8"/>
       <c r="J47" s="8"/>
@@ -1482,40 +1724,40 @@
       <c r="L47" s="8"/>
       <c r="M47" s="8"/>
     </row>
-    <row r="48" spans="1:13" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" s="1" customFormat="1" ht="136.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <v>4</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
       <c r="E48" s="8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F48" s="8"/>
       <c r="G48" s="8"/>
-      <c r="H48" s="8"/>
+      <c r="H48" s="8" t="s">
+        <v>99</v>
+      </c>
       <c r="I48" s="8"/>
       <c r="J48" s="8"/>
-      <c r="K48" s="8" t="s">
-        <v>68</v>
-      </c>
+      <c r="K48" s="8"/>
       <c r="L48" s="8"/>
       <c r="M48" s="8"/>
     </row>
-    <row r="49" spans="1:13" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <v>5</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8" t="s">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="F49" s="8"/>
       <c r="G49" s="8"/>
@@ -1523,22 +1765,22 @@
       <c r="I49" s="8"/>
       <c r="J49" s="8"/>
       <c r="K49" s="8" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="L49" s="8"/>
       <c r="M49" s="8"/>
     </row>
-    <row r="50" spans="1:13" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
         <v>6</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="C50" s="8"/>
       <c r="D50" s="8"/>
       <c r="E50" s="8" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="F50" s="8"/>
       <c r="G50" s="8"/>
@@ -1546,17 +1788,20 @@
       <c r="I50" s="8"/>
       <c r="J50" s="8"/>
       <c r="K50" s="8" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="L50" s="8"/>
       <c r="M50" s="8"/>
-    </row>
-    <row r="51" spans="1:13" s="1" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O50" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" s="1" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>7</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C51" s="8"/>
       <c r="D51" s="8"/>
@@ -1569,17 +1814,17 @@
       <c r="I51" s="8"/>
       <c r="J51" s="8"/>
       <c r="K51" s="8" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="L51" s="8"/>
       <c r="M51" s="8"/>
     </row>
-    <row r="52" spans="1:13" s="1" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" s="1" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
         <v>8</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
@@ -1592,212 +1837,284 @@
       <c r="I52" s="8"/>
       <c r="J52" s="8"/>
       <c r="K52" s="8" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="L52" s="8"/>
       <c r="M52" s="8"/>
     </row>
-    <row r="53" spans="1:13" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" s="1" customFormat="1" ht="177.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
         <v>9</v>
       </c>
-      <c r="B53" s="8"/>
+      <c r="B53" s="8" t="s">
+        <v>61</v>
+      </c>
       <c r="C53" s="8"/>
       <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
+      <c r="E53" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F53" s="8"/>
       <c r="G53" s="8"/>
       <c r="H53" s="8"/>
       <c r="I53" s="8"/>
       <c r="J53" s="8"/>
-      <c r="K53" s="8"/>
+      <c r="K53" s="8" t="s">
+        <v>106</v>
+      </c>
       <c r="L53" s="8"/>
       <c r="M53" s="8"/>
     </row>
-    <row r="54" spans="1:13" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <v>10</v>
       </c>
-      <c r="B54" s="8"/>
+      <c r="B54" s="8" t="s">
+        <v>62</v>
+      </c>
       <c r="C54" s="8"/>
       <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
+      <c r="E54" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F54" s="8"/>
       <c r="G54" s="8"/>
       <c r="H54" s="8"/>
       <c r="I54" s="8"/>
       <c r="J54" s="8"/>
-      <c r="K54" s="8"/>
+      <c r="K54" s="8" t="s">
+        <v>107</v>
+      </c>
       <c r="L54" s="8"/>
       <c r="M54" s="8"/>
     </row>
-    <row r="55" spans="1:13" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <v>11</v>
       </c>
-      <c r="B55" s="8"/>
+      <c r="B55" s="8" t="s">
+        <v>63</v>
+      </c>
       <c r="C55" s="8"/>
       <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="8"/>
-      <c r="G55" s="8"/>
+      <c r="E55" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="F55" s="22"/>
+      <c r="G55" s="23"/>
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
       <c r="J55" s="8"/>
-      <c r="K55" s="8"/>
+      <c r="K55" s="8" t="s">
+        <v>108</v>
+      </c>
       <c r="L55" s="8"/>
       <c r="M55" s="8"/>
     </row>
-    <row r="56" spans="1:13" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
         <v>12</v>
       </c>
-      <c r="B56" s="8"/>
+      <c r="B56" s="8" t="s">
+        <v>64</v>
+      </c>
       <c r="C56" s="8"/>
       <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
+      <c r="E56" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F56" s="8"/>
       <c r="G56" s="8"/>
       <c r="H56" s="8"/>
       <c r="I56" s="8"/>
       <c r="J56" s="8"/>
-      <c r="K56" s="8"/>
+      <c r="K56" s="8" t="s">
+        <v>109</v>
+      </c>
       <c r="L56" s="8"/>
       <c r="M56" s="8"/>
     </row>
-    <row r="57" spans="1:13" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" s="1" customFormat="1" ht="163.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
         <v>13</v>
       </c>
-      <c r="B57" s="8"/>
+      <c r="B57" s="8" t="s">
+        <v>65</v>
+      </c>
       <c r="C57" s="8"/>
       <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
+      <c r="E57" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F57" s="8"/>
       <c r="G57" s="8"/>
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
       <c r="J57" s="8"/>
-      <c r="K57" s="8"/>
+      <c r="K57" s="8" t="s">
+        <v>110</v>
+      </c>
       <c r="L57" s="8"/>
       <c r="M57" s="8"/>
     </row>
-    <row r="58" spans="1:13" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
         <v>14</v>
       </c>
-      <c r="B58" s="8"/>
+      <c r="B58" s="8" t="s">
+        <v>66</v>
+      </c>
       <c r="C58" s="8"/>
       <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
+      <c r="E58" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F58" s="8"/>
       <c r="G58" s="8"/>
       <c r="H58" s="8"/>
       <c r="I58" s="8"/>
       <c r="J58" s="8"/>
-      <c r="K58" s="8"/>
+      <c r="K58" s="8" t="s">
+        <v>111</v>
+      </c>
       <c r="L58" s="8"/>
       <c r="M58" s="8"/>
     </row>
-    <row r="59" spans="1:13" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
         <v>15</v>
       </c>
-      <c r="B59" s="8"/>
+      <c r="B59" s="8" t="s">
+        <v>67</v>
+      </c>
       <c r="C59" s="8"/>
       <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
+      <c r="E59" s="8" t="s">
+        <v>10</v>
+      </c>
       <c r="F59" s="8"/>
       <c r="G59" s="8"/>
       <c r="H59" s="8"/>
       <c r="I59" s="8"/>
       <c r="J59" s="8"/>
-      <c r="K59" s="8"/>
+      <c r="K59" s="8" t="s">
+        <v>112</v>
+      </c>
       <c r="L59" s="8"/>
       <c r="M59" s="8"/>
     </row>
-    <row r="60" spans="1:13" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
         <v>16</v>
       </c>
-      <c r="B60" s="8"/>
+      <c r="B60" s="8" t="s">
+        <v>68</v>
+      </c>
       <c r="C60" s="8"/>
       <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
+      <c r="E60" s="8" t="s">
+        <v>10</v>
+      </c>
       <c r="F60" s="8"/>
       <c r="G60" s="8"/>
       <c r="H60" s="8"/>
       <c r="I60" s="8"/>
       <c r="J60" s="8"/>
-      <c r="K60" s="8"/>
+      <c r="K60" s="8" t="s">
+        <v>113</v>
+      </c>
       <c r="L60" s="8"/>
       <c r="M60" s="8"/>
     </row>
-    <row r="61" spans="1:13" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
         <v>17</v>
       </c>
-      <c r="B61" s="8"/>
+      <c r="B61" s="8" t="s">
+        <v>69</v>
+      </c>
       <c r="C61" s="8"/>
       <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
+      <c r="E61" s="8" t="s">
+        <v>10</v>
+      </c>
       <c r="F61" s="8"/>
       <c r="G61" s="8"/>
       <c r="H61" s="8"/>
       <c r="I61" s="8"/>
       <c r="J61" s="8"/>
-      <c r="K61" s="8"/>
+      <c r="K61" s="8" t="s">
+        <v>114</v>
+      </c>
       <c r="L61" s="8"/>
       <c r="M61" s="8"/>
     </row>
-    <row r="62" spans="1:13" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <v>18</v>
       </c>
-      <c r="B62" s="8"/>
+      <c r="B62" s="8" t="s">
+        <v>70</v>
+      </c>
       <c r="C62" s="8"/>
       <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
+      <c r="E62" s="8" t="s">
+        <v>11</v>
+      </c>
       <c r="F62" s="8"/>
       <c r="G62" s="8"/>
       <c r="H62" s="8"/>
       <c r="I62" s="8"/>
       <c r="J62" s="8"/>
-      <c r="K62" s="8"/>
+      <c r="K62" s="8" t="s">
+        <v>115</v>
+      </c>
       <c r="L62" s="8"/>
       <c r="M62" s="8"/>
     </row>
-    <row r="63" spans="1:13" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
         <v>19</v>
       </c>
-      <c r="B63" s="8"/>
+      <c r="B63" s="8" t="s">
+        <v>71</v>
+      </c>
       <c r="C63" s="8"/>
       <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
+      <c r="E63" s="8" t="s">
+        <v>11</v>
+      </c>
       <c r="F63" s="8"/>
       <c r="G63" s="8"/>
       <c r="H63" s="8"/>
       <c r="I63" s="8"/>
       <c r="J63" s="8"/>
-      <c r="K63" s="8"/>
+      <c r="K63" s="8" t="s">
+        <v>116</v>
+      </c>
       <c r="L63" s="8"/>
       <c r="M63" s="8"/>
     </row>
-    <row r="64" spans="1:13" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <v>20</v>
       </c>
-      <c r="B64" s="8"/>
+      <c r="B64" s="8" t="s">
+        <v>72</v>
+      </c>
       <c r="C64" s="8"/>
       <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
+      <c r="E64" s="8" t="s">
+        <v>12</v>
+      </c>
       <c r="F64" s="8"/>
       <c r="G64" s="8"/>
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
       <c r="J64" s="8"/>
-      <c r="K64" s="8"/>
+      <c r="K64" s="8" t="s">
+        <v>117</v>
+      </c>
       <c r="L64" s="8"/>
       <c r="M64" s="8"/>
     </row>
@@ -1805,208 +2122,394 @@
       <c r="A65" s="5">
         <v>21</v>
       </c>
-      <c r="B65" s="8"/>
+      <c r="B65" s="8" t="s">
+        <v>73</v>
+      </c>
       <c r="C65" s="8"/>
       <c r="D65" s="8"/>
-      <c r="E65" s="8"/>
+      <c r="E65" s="8" t="s">
+        <v>12</v>
+      </c>
       <c r="F65" s="8"/>
       <c r="G65" s="8"/>
       <c r="H65" s="8"/>
       <c r="I65" s="8"/>
       <c r="J65" s="8"/>
-      <c r="K65" s="8"/>
+      <c r="K65" s="8" t="s">
+        <v>118</v>
+      </c>
       <c r="L65" s="8"/>
       <c r="M65" s="8"/>
     </row>
-    <row r="66" spans="1:13" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" s="1" customFormat="1" ht="121.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
         <v>22</v>
       </c>
-      <c r="B66" s="8"/>
+      <c r="B66" s="8" t="s">
+        <v>74</v>
+      </c>
       <c r="C66" s="8"/>
       <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
+      <c r="E66" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="F66" s="8"/>
       <c r="G66" s="8"/>
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
       <c r="J66" s="8"/>
-      <c r="K66" s="8"/>
+      <c r="K66" s="8" t="s">
+        <v>119</v>
+      </c>
       <c r="L66" s="8"/>
       <c r="M66" s="8"/>
     </row>
-    <row r="67" spans="1:13" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" s="1" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
         <v>23</v>
       </c>
-      <c r="B67" s="8"/>
+      <c r="B67" s="8" t="s">
+        <v>75</v>
+      </c>
       <c r="C67" s="8"/>
       <c r="D67" s="8"/>
-      <c r="E67" s="8"/>
+      <c r="E67" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="F67" s="8"/>
       <c r="G67" s="8"/>
       <c r="H67" s="8"/>
       <c r="I67" s="8"/>
       <c r="J67" s="8"/>
-      <c r="K67" s="8"/>
+      <c r="K67" s="8" t="s">
+        <v>120</v>
+      </c>
       <c r="L67" s="8"/>
       <c r="M67" s="8"/>
     </row>
-    <row r="68" spans="1:13" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" s="1" customFormat="1" ht="117.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
         <v>24</v>
       </c>
-      <c r="B68" s="8"/>
+      <c r="B68" s="8" t="s">
+        <v>76</v>
+      </c>
       <c r="C68" s="8"/>
       <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
+      <c r="E68" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="F68" s="8"/>
       <c r="G68" s="8"/>
       <c r="H68" s="8"/>
       <c r="I68" s="8"/>
       <c r="J68" s="8"/>
-      <c r="K68" s="8"/>
+      <c r="K68" s="8" t="s">
+        <v>121</v>
+      </c>
       <c r="L68" s="8"/>
       <c r="M68" s="8"/>
     </row>
-    <row r="69" spans="1:13" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" s="1" customFormat="1" ht="133.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
         <v>25</v>
       </c>
-      <c r="B69" s="8"/>
+      <c r="B69" s="8" t="s">
+        <v>77</v>
+      </c>
       <c r="C69" s="8"/>
       <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
+      <c r="E69" s="8" t="s">
+        <v>14</v>
+      </c>
       <c r="F69" s="8"/>
       <c r="G69" s="8"/>
       <c r="H69" s="8"/>
       <c r="I69" s="8"/>
       <c r="J69" s="8"/>
-      <c r="K69" s="8"/>
+      <c r="K69" s="8" t="s">
+        <v>122</v>
+      </c>
       <c r="L69" s="8"/>
       <c r="M69" s="8"/>
     </row>
-    <row r="70" spans="1:13" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" s="1" customFormat="1" ht="133.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
         <v>26</v>
       </c>
-      <c r="B70" s="8"/>
+      <c r="B70" s="8" t="s">
+        <v>78</v>
+      </c>
       <c r="C70" s="8"/>
       <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
+      <c r="E70" s="8" t="s">
+        <v>14</v>
+      </c>
       <c r="F70" s="8"/>
       <c r="G70" s="8"/>
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
       <c r="J70" s="8"/>
-      <c r="K70" s="8"/>
+      <c r="K70" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="L70" s="8"/>
       <c r="M70" s="8"/>
     </row>
-    <row r="71" spans="1:13" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" s="1" customFormat="1" ht="141" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
         <v>27</v>
       </c>
-      <c r="B71" s="8"/>
+      <c r="B71" s="8" t="s">
+        <v>79</v>
+      </c>
       <c r="C71" s="8"/>
       <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
+      <c r="E71" s="8" t="s">
+        <v>14</v>
+      </c>
       <c r="F71" s="8"/>
       <c r="G71" s="8"/>
       <c r="H71" s="8"/>
       <c r="I71" s="8"/>
       <c r="J71" s="8"/>
-      <c r="K71" s="8"/>
+      <c r="K71" s="8" t="s">
+        <v>124</v>
+      </c>
       <c r="L71" s="8"/>
       <c r="M71" s="8"/>
     </row>
-    <row r="72" spans="1:13" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" s="1" customFormat="1" ht="114.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
         <v>28</v>
       </c>
-      <c r="B72" s="8"/>
+      <c r="B72" s="8" t="s">
+        <v>125</v>
+      </c>
       <c r="C72" s="8"/>
       <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
+      <c r="E72" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F72" s="8"/>
       <c r="G72" s="8"/>
       <c r="H72" s="8"/>
       <c r="I72" s="8"/>
       <c r="J72" s="8"/>
-      <c r="K72" s="8"/>
+      <c r="K72" s="8" t="s">
+        <v>126</v>
+      </c>
       <c r="L72" s="8"/>
       <c r="M72" s="8"/>
     </row>
-    <row r="73" spans="1:13" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" s="1" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
-        <v>29</v>
-      </c>
-      <c r="B73" s="8"/>
+        <v>30</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>127</v>
+      </c>
       <c r="C73" s="8"/>
       <c r="D73" s="8"/>
-      <c r="E73" s="8"/>
+      <c r="E73" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="F73" s="8"/>
       <c r="G73" s="8"/>
       <c r="H73" s="8"/>
       <c r="I73" s="8"/>
       <c r="J73" s="8"/>
-      <c r="K73" s="8"/>
+      <c r="K73" s="8" t="s">
+        <v>128</v>
+      </c>
       <c r="L73" s="8"/>
       <c r="M73" s="8"/>
     </row>
-    <row r="74" spans="1:13" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" s="1" customFormat="1" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
-        <v>30</v>
-      </c>
-      <c r="B74" s="8"/>
+        <v>31</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>136</v>
+      </c>
       <c r="C74" s="8"/>
       <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="8"/>
-      <c r="G74" s="8"/>
+      <c r="E74" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="F74" s="22"/>
+      <c r="G74" s="23"/>
       <c r="H74" s="8"/>
       <c r="I74" s="8"/>
       <c r="J74" s="8"/>
-      <c r="K74" s="8"/>
+      <c r="K74" s="8" t="s">
+        <v>129</v>
+      </c>
       <c r="L74" s="8"/>
       <c r="M74" s="8"/>
     </row>
-    <row r="75" spans="1:13" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" s="1" customFormat="1" ht="112.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
-        <v>31</v>
-      </c>
-      <c r="B75" s="8"/>
+        <v>32</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>137</v>
+      </c>
       <c r="C75" s="8"/>
       <c r="D75" s="8"/>
-      <c r="E75" s="8"/>
-      <c r="F75" s="8"/>
-      <c r="G75" s="8"/>
+      <c r="E75" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="F75" s="22"/>
+      <c r="G75" s="23"/>
       <c r="H75" s="8"/>
       <c r="I75" s="8"/>
       <c r="J75" s="8"/>
-      <c r="K75" s="8"/>
+      <c r="K75" s="8" t="s">
+        <v>130</v>
+      </c>
       <c r="L75" s="8"/>
       <c r="M75" s="8"/>
     </row>
-    <row r="76" spans="1:13" s="1" customFormat="1" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" s="1" customFormat="1" ht="111.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
-        <v>32</v>
-      </c>
-      <c r="B76" s="8"/>
+        <v>33</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>138</v>
+      </c>
       <c r="C76" s="8"/>
       <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
+      <c r="E76" s="8" t="s">
+        <v>10</v>
+      </c>
       <c r="F76" s="8"/>
       <c r="G76" s="8"/>
       <c r="H76" s="8"/>
       <c r="I76" s="8"/>
       <c r="J76" s="8"/>
-      <c r="K76" s="8"/>
+      <c r="K76" s="8" t="s">
+        <v>131</v>
+      </c>
       <c r="L76" s="8"/>
       <c r="M76" s="8"/>
     </row>
+    <row r="77" spans="1:13" ht="110.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="5">
+        <v>34</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C77" s="8"/>
+      <c r="D77" s="8"/>
+      <c r="E77" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F77" s="8"/>
+      <c r="G77" s="8"/>
+      <c r="H77" s="8"/>
+      <c r="I77" s="8"/>
+      <c r="J77" s="8"/>
+      <c r="K77" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="L77" s="8"/>
+      <c r="M77" s="8"/>
+    </row>
+    <row r="78" spans="1:13" ht="111.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="5">
+        <v>35</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C78" s="8"/>
+      <c r="D78" s="8"/>
+      <c r="E78" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F78" s="8"/>
+      <c r="G78" s="8"/>
+      <c r="H78" s="8"/>
+      <c r="I78" s="8"/>
+      <c r="J78" s="8"/>
+      <c r="K78" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="L78" s="8"/>
+      <c r="M78" s="8"/>
+    </row>
+    <row r="79" spans="1:13" ht="119.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="5">
+        <v>36</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C79" s="8"/>
+      <c r="D79" s="8"/>
+      <c r="E79" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F79" s="8"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="8"/>
+      <c r="I79" s="8"/>
+      <c r="J79" s="8"/>
+      <c r="K79" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="L79" s="8"/>
+      <c r="M79" s="8"/>
+    </row>
+    <row r="80" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="7"/>
+      <c r="B80" s="7"/>
+      <c r="C80" s="7"/>
+      <c r="D80" s="7"/>
+      <c r="E80" s="7"/>
+      <c r="F80" s="7"/>
+      <c r="G80" s="7"/>
+      <c r="H80" s="7"/>
+      <c r="I80" s="7"/>
+      <c r="J80" s="7"/>
+      <c r="K80" s="7"/>
+      <c r="L80" s="7"/>
+      <c r="M80" s="7"/>
+    </row>
+    <row r="81" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="7"/>
+      <c r="B81" s="7"/>
+      <c r="C81" s="7"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="7"/>
+      <c r="F81" s="7"/>
+      <c r="G81" s="7"/>
+      <c r="H81" s="7"/>
+      <c r="I81" s="7"/>
+      <c r="J81" s="7"/>
+      <c r="K81" s="7"/>
+      <c r="L81" s="7"/>
+      <c r="M81" s="7"/>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82" s="6"/>
+      <c r="B82" s="6"/>
+      <c r="C82" s="6"/>
+      <c r="D82" s="6"/>
+      <c r="E82" s="6"/>
+      <c r="F82" s="6"/>
+      <c r="G82" s="6"/>
+      <c r="H82" s="6"/>
+      <c r="I82" s="6"/>
+      <c r="J82" s="6"/>
+      <c r="K82" s="6"/>
+      <c r="L82" s="6"/>
+      <c r="M82" s="6"/>
+    </row>
   </sheetData>
-  <mergeCells count="198">
+  <mergeCells count="210">
     <mergeCell ref="B75:D75"/>
     <mergeCell ref="E75:G75"/>
     <mergeCell ref="H75:J75"/>
@@ -2168,6 +2671,7 @@
     <mergeCell ref="E32:G32"/>
     <mergeCell ref="H32:J32"/>
     <mergeCell ref="K32:M32"/>
+    <mergeCell ref="K38:M38"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="E33:G33"/>
     <mergeCell ref="H33:J33"/>
@@ -2180,15 +2684,6 @@
     <mergeCell ref="E35:G35"/>
     <mergeCell ref="H35:J35"/>
     <mergeCell ref="K35:M35"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="K36:M36"/>
-    <mergeCell ref="K37:M37"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="K38:M38"/>
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="E41:G41"/>
     <mergeCell ref="H41:J41"/>
@@ -2205,6 +2700,26 @@
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="E37:G37"/>
     <mergeCell ref="H37:J37"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="K37:M37"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="E77:G77"/>
+    <mergeCell ref="H77:J77"/>
+    <mergeCell ref="K77:M77"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="E78:G78"/>
+    <mergeCell ref="H78:J78"/>
+    <mergeCell ref="K78:M78"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="E79:G79"/>
+    <mergeCell ref="H79:J79"/>
+    <mergeCell ref="K79:M79"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
